--- a/easy_normal_answered.xlsx
+++ b/easy_normal_answered.xlsx
@@ -457,7 +457,7 @@
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="85" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">

--- a/easy_normal_answered.xlsx
+++ b/easy_normal_answered.xlsx
@@ -457,7 +457,7 @@
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="85" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
